--- a/AtchisonRegime/Outputs/Japan/MSCI_Europe/df_regSummary_MSCI_Europe.xlsx
+++ b/AtchisonRegime/Outputs/Japan/MSCI_Europe/df_regSummary_MSCI_Europe.xlsx
@@ -545,7 +545,7 @@
         <v>11.6865661939146</v>
       </c>
       <c r="K2" t="n">
-        <v>27.61904761904762</v>
+        <v>27.53164556962026</v>
       </c>
       <c r="L2" t="n">
         <v>9</v>
@@ -603,7 +603,7 @@
         <v>9.70751728527032</v>
       </c>
       <c r="K3" t="n">
-        <v>20.95238095238095</v>
+        <v>20.88607594936709</v>
       </c>
       <c r="L3" t="n">
         <v>12</v>
@@ -661,7 +661,7 @@
         <v>8.087478763970051</v>
       </c>
       <c r="K4" t="n">
-        <v>20.31746031746032</v>
+        <v>20.25316455696203</v>
       </c>
       <c r="L4" t="n">
         <v>9</v>
@@ -704,13 +704,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2734960896943699</v>
+        <v>0.2892377204671128</v>
       </c>
       <c r="H5" t="n">
-        <v>3.754590581871229</v>
+        <v>3.738667690426607</v>
       </c>
       <c r="I5" t="n">
         <v>-10.4724059948479</v>
@@ -719,16 +719,16 @@
         <v>7.84520022895685</v>
       </c>
       <c r="K5" t="n">
-        <v>31.11111111111111</v>
+        <v>31.32911392405063</v>
       </c>
       <c r="L5" t="n">
         <v>13</v>
       </c>
       <c r="M5" t="n">
-        <v>7.538461538461538</v>
+        <v>7.615384615384615</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02275559171810671</v>
+        <v>0.02432853563840072</v>
       </c>
       <c r="O5" t="n">
         <v>-0.2848963380678321</v>
